--- a/administrative_forms/025_it_support_authorization_form--administrative_forms.xlsx
+++ b/administrative_forms/025_it_support_authorization_form--administrative_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,8 +431,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -510,18 +510,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>it_support_authorization_form_page_1</t>
+          <t>employee_info</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>it_support_authorization_form_page_1</t>
+          <t>Employee Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -533,18 +533,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>it_support_authorization_form_page_1</t>
+          <t>availability</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>it_support_authorization_form_page_1</t>
+          <t>Availability and Priorities</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -556,12 +556,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>it_support_authorization_form_page_1</t>
+          <t>additional_issues</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>it_support_authorization_form_page_1</t>
+          <t>Additional Issues</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -574,23 +574,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>it_support_authorization_form_page_1</t>
+          <t>deadline</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>it_support_authorization_form_page_1</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -602,12 +602,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>it_support_authorization_form_page_1</t>
+          <t>expected_outcome</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>it_support_authorization_form_page_1</t>
+          <t>Expected Outcome</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -625,41 +625,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>it_support_authorization_form_page_2</t>
+          <t>authorization</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>it_support_authorization_form_page_2</t>
+          <t>Authorization</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>it_support_authorization_form_page_3</t>
+          <t>additional_info</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>it_support_authorization_form_page_3</t>
+          <t>Additional Information or Attachments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
